--- a/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-medicationstatement-injection.xlsx
+++ b/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-medicationstatement-injection.xlsx
@@ -81,13 +81,13 @@
     <t>Description</t>
   </si>
   <si>
-    <t>このProfileは服薬状況を示すものであり，診療情報提供書や退院サマリーなどの他の文書と組み合わせて用いられる。</t>
+    <t>このProfileは服薬状況を示すものであり、診療情報提供書や退院サマリーなどの他の文書と組み合わせて用いられる。</t>
   </si>
   <si>
     <t>Purpose</t>
   </si>
   <si>
-    <t>このProfileは診療情報提供書や退院サマリーなどの医療文書内で服薬情報について記載するために用いられる。このResourceは薬剤処方や，調剤情報，薬剤投与実施情報としては用いられず，それぞれMedicationRequest, MedicationDispense, MedicationAdministrationが用いられる。</t>
+    <t>このProfileは診療情報提供書や退院サマリーなどの医療文書内で服薬情報について記載するために用いられる。このResourceは薬剤処方や、調剤情報、薬剤投与実施情報としては用いられず、それぞれMedicationRequest, MedicationDispense, MedicationAdministrationが用いられる。</t>
   </si>
   <si>
     <t>Copyright</t>
@@ -501,7 +501,7 @@
   </si>
   <si>
     <t>このインスタンスが外部から参照されるために使われるIDである。それ以外に任意のIDを付与してもよい。
-このIDは業務手順によって定められた処方オーダーに対して、直接的なURL参照が適切でない場合も含めて関連付けるために使われる。この業務手順のIDは実施者によって割り当てられたものであり、リソースが更新されたりサーバからサーバに転送されたとしても固定のものとして存続する。</t>
+このIDは業務手順によって定められた処方オーダーに対して、直接的なURL参照が適切でない場合も含めて関連付けるために使われる。この業務手順のIDは実施者によって割り当てられたものであり、リソースが更新されたりサーバーからサーバーに転送されたとしても固定のものとして存続する。</t>
   </si>
   <si>
     <t>これは業務IDであって、リソースに対するIDではない。</t>
@@ -966,7 +966,7 @@
 </t>
   </si>
   <si>
-    <t>投与理由，対象疾患についてのコード</t>
+    <t>投与理由、対象疾患についてのコード</t>
   </si>
   <si>
     <t>用語システムによって定義されたコードへの参照。 / A reference to a code defined by a terminology system.</t>
@@ -1059,7 +1059,7 @@
 </t>
   </si>
   <si>
-    <t>この薬剤がどのように服用されたのか，服用すべきだったのかを示す情報</t>
+    <t>この薬剤がどのように服用されたのか、服用すべきだったのかを示す情報</t>
   </si>
   <si>
     <t>患者にこの薬剤がどのように服用すべきかを示す情報</t>
@@ -1742,7 +1742,7 @@
     <t>投与経路</t>
   </si>
   <si>
-    <t>投与経路の一般的パターンに全てのターミノロジが適応しているわけではない。情報モデルはCodeableConceptではなく、直接Codingをを使用してテキストやコーディング、翻訳、そしてエレメントと事前条件、事後条件の関係について管理するためにその構造を提示する必要がある。  
+    <t>投与経路の一般的パターンに全てのターミノロジが適応しているわけではない。情報モデルはCodeableConceptではなく、直接`Coding`を使用してテキストや`Coding`、翻訳、そしてエレメントと事前条件、事後条件の関係について管理するためにその構造を提示する必要がある。
 【JP Core仕様】HL7表0162をベースにした投与経路コードを使用することが望ましいが、ローカルコードも使用可能。</t>
   </si>
   <si>
@@ -1857,7 +1857,7 @@
     <t>投与⽅法に対応するJAMI 用法コード表基本用法１桁コードを識別するURI。</t>
   </si>
   <si>
-    <t>コードは臨時で列記したものや、コードのリストからSNOMED CTのように公式に定義されたものまである（HL7 v3 core principle を参照)。FHIR自体ではコーディング規約を定めてはいないし、意味を暗示するために利用されない(SHALL NOT)。一般的に UserSelected = trueの場合には一つのコードシステムが使われる。</t>
+    <t>コードは臨時で列記したものや、コードのリストからSNOMED CTのように公式に定義されたものまである（HL7 v3 core principle を参照)。FHIR自体ではコード化に関する規約を定めてはいないし、意味を暗示するために利用されない(SHALL NOT)。一般的に UserSelected = trueの場合には一つのコードシステムが使われる。</t>
   </si>
   <si>
     <t>他のコードシステムへの変換や代替のコードシステムを使ってエンコードしてもよい。</t>
@@ -2079,7 +2079,7 @@
     <t>力価区分</t>
   </si>
   <si>
-    <t>投与速度・量の一般的パターンに全てのターミノロジが適応しているわけではない。情報モデルはCodeableConceptではなく、直接Codingをを使用してテキストやコーディング、翻訳、そしてエレメントと事前条件、事後条件の関係について管理するためにその構造を提示する必要がある。</t>
+    <t>投与速度・量の一般的パターンに全てのターミノロジが適応しているわけではない。情報モデルはCodeableConceptではなく、直接`Coding`を使用してテキストや`Coding`、翻訳、そしてエレメントと事前条件、事後条件の関係について管理するためにその構造を提示する必要がある。</t>
   </si>
   <si>
     <t>このtypeに値が指定されていなければ、"ordered"であることが想定される。</t>
